--- a/db/A7XLK-2402-污水處理統計.xlsx
+++ b/db/A7XLK-2402-污水處理統計.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10" conformance="strict">
+<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{B86D7B47-33B6-3546-A675-A7EEF220781B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B0DDD9C7-CE5F-B848-AD5B-B1BD7E74C414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3580" yWindow="5080" windowWidth="39920" windowHeight="22540" activeTab="2"/>
+    <workbookView xWindow="1200" yWindow="500" windowWidth="27120" windowHeight="22540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="用戶接管普及率及污水處理率統計一覽表" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="180" uniqueCount="77">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="189" uniqueCount="77">
   <si>
     <t>用戶接管普及率及污水處理率統計一覽表(依本月人口資料)</t>
   </si>
@@ -414,7 +414,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="176" formatCode="&quot; &quot;#,##0.00&quot; &quot;;&quot;-&quot;#,##0.00&quot; &quot;;&quot; -&quot;00&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
     <numFmt numFmtId="177" formatCode="0.00&quot; &quot;;[Red]&quot;(&quot;0.00&quot;)&quot;"/>
@@ -434,7 +434,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="·s²Ó©úÅé"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="12"/>
@@ -493,7 +492,6 @@
     <font>
       <sz val="9"/>
       <name val="·s²Ó©úÅé"/>
-      <charset val="136"/>
     </font>
     <font>
       <b/>
@@ -772,18 +770,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -834,6 +820,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -846,27 +856,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="一般" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="一般 2" xfId="1"/>
-    <cellStyle name="一般 2 2" xfId="2"/>
-    <cellStyle name="一般 2 3" xfId="3"/>
-    <cellStyle name="一般 3" xfId="4"/>
-    <cellStyle name="一般 3 2" xfId="5"/>
-    <cellStyle name="千分位 2" xfId="6"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="一般 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="一般 2 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="一般 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="一般 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="千分位 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1897,7 +1895,402 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2000" baseline="0%">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>整體污水處理率合計</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65%"/>
+                  <a:lumOff val="35%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表1!$C$103</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>整體污水處理率合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75%"/>
+                        <a:lumOff val="25%"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35%"/>
+                          <a:lumOff val="65%"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$B$104:$B$110</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>新北市</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台北市</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>高雄市</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>台中市</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>桃園市</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>台南市</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>臺灣省</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$C$104:$C$110</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" "</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>91.902786635166137</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>86.462423494897067</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.751112086333805</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67.834300851439579</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67.185936956006003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>57.513026780986408</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40.749916828926217</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-82F8-7646-BB7F-FC4CF28172F5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="400338863"/>
+        <c:axId val="400349151"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="400338863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15%"/>
+                <a:lumOff val="85%"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="400349151"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="400349151"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0.00&quot; &quot;" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="400338863"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15%"/>
+          <a:lumOff val="85%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+    <a:lumOff val="20%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+    <a:lumOff val="40%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+    <a:lumOff val="30%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+    <a:lumOff val="50%"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2442,6 +2835,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75%"/>
+        <a:lumOff val="25%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65%"/>
+          <a:lumOff val="35%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5%"/>
+            <a:lumOff val="95%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75%"/>
+            <a:lumOff val="25%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0%"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:twoCellAnchor>
@@ -2480,11 +3376,47 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1261D5A-F4A2-6A40-97BB-6AA1C2F1E623}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://purl.oclc.org/ooxml/drawingml/chart">
+          <c:chart xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDateIso="2021-08-14T06:32:07.29000016115605800" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="24">
+<pivotCacheDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDateIso="2021-08-14T06:32:07.29000016115605800" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="24" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B32:C56" sheet="工作表1"/>
   </cacheSource>
@@ -2656,7 +3588,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" name="樞紐分析表1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F32:G57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -3121,9 +4053,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="2" max="5" width="28.1640625" customWidth="1"/>
@@ -3131,13 +4063,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -3145,18 +4077,18 @@
       </c>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
     </row>
     <row r="4" spans="1:5" s="1" customFormat="1" ht="42.75" customHeight="1">
-      <c r="A4" s="8"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3595,47 +4527,46 @@
         <v>65.784870162263701</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15"/>
     <row r="31" spans="1:5" ht="18">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="6" customFormat="1" ht="36" customHeight="1">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
     </row>
     <row r="33" spans="1:5" s="6" customFormat="1" ht="60.75" customHeight="1">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
     </row>
     <row r="34" spans="1:5" s="6" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
     </row>
     <row r="35" spans="1:5" s="6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3655,904 +4586,904 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35" style="27" customWidth="1"/>
-    <col min="2" max="2" width="26" style="28" customWidth="1"/>
-    <col min="3" max="3" width="25.5" style="28" customWidth="1"/>
-    <col min="4" max="4" width="29.5" style="28" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" style="28" customWidth="1"/>
-    <col min="6" max="256" width="11.83203125" style="11" customWidth="1"/>
-    <col min="257" max="257" width="35" style="11" customWidth="1"/>
-    <col min="258" max="258" width="26" style="11" customWidth="1"/>
-    <col min="259" max="259" width="25.5" style="11" customWidth="1"/>
-    <col min="260" max="260" width="29.5" style="11" customWidth="1"/>
-    <col min="261" max="261" width="31.33203125" style="11" customWidth="1"/>
-    <col min="262" max="512" width="11.83203125" style="11" customWidth="1"/>
-    <col min="513" max="513" width="35" style="11" customWidth="1"/>
-    <col min="514" max="514" width="26" style="11" customWidth="1"/>
-    <col min="515" max="515" width="25.5" style="11" customWidth="1"/>
-    <col min="516" max="516" width="29.5" style="11" customWidth="1"/>
-    <col min="517" max="517" width="31.33203125" style="11" customWidth="1"/>
-    <col min="518" max="768" width="11.83203125" style="11" customWidth="1"/>
-    <col min="769" max="769" width="35" style="11" customWidth="1"/>
-    <col min="770" max="770" width="26" style="11" customWidth="1"/>
-    <col min="771" max="771" width="25.5" style="11" customWidth="1"/>
-    <col min="772" max="772" width="29.5" style="11" customWidth="1"/>
-    <col min="773" max="773" width="31.33203125" style="11" customWidth="1"/>
-    <col min="774" max="1024" width="11.83203125" style="11" customWidth="1"/>
-    <col min="1025" max="1025" width="35" style="11" customWidth="1"/>
-    <col min="1026" max="1026" width="26" style="11" customWidth="1"/>
-    <col min="1027" max="1027" width="25.5" style="11" customWidth="1"/>
-    <col min="1028" max="1028" width="29.5" style="11" customWidth="1"/>
-    <col min="1029" max="1029" width="31.33203125" style="11" customWidth="1"/>
-    <col min="1030" max="1280" width="11.83203125" style="11" customWidth="1"/>
-    <col min="1281" max="1281" width="35" style="11" customWidth="1"/>
-    <col min="1282" max="1282" width="26" style="11" customWidth="1"/>
-    <col min="1283" max="1283" width="25.5" style="11" customWidth="1"/>
-    <col min="1284" max="1284" width="29.5" style="11" customWidth="1"/>
-    <col min="1285" max="1285" width="31.33203125" style="11" customWidth="1"/>
-    <col min="1286" max="1536" width="11.83203125" style="11" customWidth="1"/>
-    <col min="1537" max="1537" width="35" style="11" customWidth="1"/>
-    <col min="1538" max="1538" width="26" style="11" customWidth="1"/>
-    <col min="1539" max="1539" width="25.5" style="11" customWidth="1"/>
-    <col min="1540" max="1540" width="29.5" style="11" customWidth="1"/>
-    <col min="1541" max="1541" width="31.33203125" style="11" customWidth="1"/>
-    <col min="1542" max="1792" width="11.83203125" style="11" customWidth="1"/>
-    <col min="1793" max="1793" width="35" style="11" customWidth="1"/>
-    <col min="1794" max="1794" width="26" style="11" customWidth="1"/>
-    <col min="1795" max="1795" width="25.5" style="11" customWidth="1"/>
-    <col min="1796" max="1796" width="29.5" style="11" customWidth="1"/>
-    <col min="1797" max="1797" width="31.33203125" style="11" customWidth="1"/>
-    <col min="1798" max="2048" width="11.83203125" style="11" customWidth="1"/>
-    <col min="2049" max="2049" width="35" style="11" customWidth="1"/>
-    <col min="2050" max="2050" width="26" style="11" customWidth="1"/>
-    <col min="2051" max="2051" width="25.5" style="11" customWidth="1"/>
-    <col min="2052" max="2052" width="29.5" style="11" customWidth="1"/>
-    <col min="2053" max="2053" width="31.33203125" style="11" customWidth="1"/>
-    <col min="2054" max="2304" width="11.83203125" style="11" customWidth="1"/>
-    <col min="2305" max="2305" width="35" style="11" customWidth="1"/>
-    <col min="2306" max="2306" width="26" style="11" customWidth="1"/>
-    <col min="2307" max="2307" width="25.5" style="11" customWidth="1"/>
-    <col min="2308" max="2308" width="29.5" style="11" customWidth="1"/>
-    <col min="2309" max="2309" width="31.33203125" style="11" customWidth="1"/>
-    <col min="2310" max="2560" width="11.83203125" style="11" customWidth="1"/>
-    <col min="2561" max="2561" width="35" style="11" customWidth="1"/>
-    <col min="2562" max="2562" width="26" style="11" customWidth="1"/>
-    <col min="2563" max="2563" width="25.5" style="11" customWidth="1"/>
-    <col min="2564" max="2564" width="29.5" style="11" customWidth="1"/>
-    <col min="2565" max="2565" width="31.33203125" style="11" customWidth="1"/>
-    <col min="2566" max="2816" width="11.83203125" style="11" customWidth="1"/>
-    <col min="2817" max="2817" width="35" style="11" customWidth="1"/>
-    <col min="2818" max="2818" width="26" style="11" customWidth="1"/>
-    <col min="2819" max="2819" width="25.5" style="11" customWidth="1"/>
-    <col min="2820" max="2820" width="29.5" style="11" customWidth="1"/>
-    <col min="2821" max="2821" width="31.33203125" style="11" customWidth="1"/>
-    <col min="2822" max="3072" width="11.83203125" style="11" customWidth="1"/>
-    <col min="3073" max="3073" width="35" style="11" customWidth="1"/>
-    <col min="3074" max="3074" width="26" style="11" customWidth="1"/>
-    <col min="3075" max="3075" width="25.5" style="11" customWidth="1"/>
-    <col min="3076" max="3076" width="29.5" style="11" customWidth="1"/>
-    <col min="3077" max="3077" width="31.33203125" style="11" customWidth="1"/>
-    <col min="3078" max="3328" width="11.83203125" style="11" customWidth="1"/>
-    <col min="3329" max="3329" width="35" style="11" customWidth="1"/>
-    <col min="3330" max="3330" width="26" style="11" customWidth="1"/>
-    <col min="3331" max="3331" width="25.5" style="11" customWidth="1"/>
-    <col min="3332" max="3332" width="29.5" style="11" customWidth="1"/>
-    <col min="3333" max="3333" width="31.33203125" style="11" customWidth="1"/>
-    <col min="3334" max="3584" width="11.83203125" style="11" customWidth="1"/>
-    <col min="3585" max="3585" width="35" style="11" customWidth="1"/>
-    <col min="3586" max="3586" width="26" style="11" customWidth="1"/>
-    <col min="3587" max="3587" width="25.5" style="11" customWidth="1"/>
-    <col min="3588" max="3588" width="29.5" style="11" customWidth="1"/>
-    <col min="3589" max="3589" width="31.33203125" style="11" customWidth="1"/>
-    <col min="3590" max="3840" width="11.83203125" style="11" customWidth="1"/>
-    <col min="3841" max="3841" width="35" style="11" customWidth="1"/>
-    <col min="3842" max="3842" width="26" style="11" customWidth="1"/>
-    <col min="3843" max="3843" width="25.5" style="11" customWidth="1"/>
-    <col min="3844" max="3844" width="29.5" style="11" customWidth="1"/>
-    <col min="3845" max="3845" width="31.33203125" style="11" customWidth="1"/>
-    <col min="3846" max="4096" width="11.83203125" style="11" customWidth="1"/>
-    <col min="4097" max="4097" width="35" style="11" customWidth="1"/>
-    <col min="4098" max="4098" width="26" style="11" customWidth="1"/>
-    <col min="4099" max="4099" width="25.5" style="11" customWidth="1"/>
-    <col min="4100" max="4100" width="29.5" style="11" customWidth="1"/>
-    <col min="4101" max="4101" width="31.33203125" style="11" customWidth="1"/>
-    <col min="4102" max="4352" width="11.83203125" style="11" customWidth="1"/>
-    <col min="4353" max="4353" width="35" style="11" customWidth="1"/>
-    <col min="4354" max="4354" width="26" style="11" customWidth="1"/>
-    <col min="4355" max="4355" width="25.5" style="11" customWidth="1"/>
-    <col min="4356" max="4356" width="29.5" style="11" customWidth="1"/>
-    <col min="4357" max="4357" width="31.33203125" style="11" customWidth="1"/>
-    <col min="4358" max="4608" width="11.83203125" style="11" customWidth="1"/>
-    <col min="4609" max="4609" width="35" style="11" customWidth="1"/>
-    <col min="4610" max="4610" width="26" style="11" customWidth="1"/>
-    <col min="4611" max="4611" width="25.5" style="11" customWidth="1"/>
-    <col min="4612" max="4612" width="29.5" style="11" customWidth="1"/>
-    <col min="4613" max="4613" width="31.33203125" style="11" customWidth="1"/>
-    <col min="4614" max="4864" width="11.83203125" style="11" customWidth="1"/>
-    <col min="4865" max="4865" width="35" style="11" customWidth="1"/>
-    <col min="4866" max="4866" width="26" style="11" customWidth="1"/>
-    <col min="4867" max="4867" width="25.5" style="11" customWidth="1"/>
-    <col min="4868" max="4868" width="29.5" style="11" customWidth="1"/>
-    <col min="4869" max="4869" width="31.33203125" style="11" customWidth="1"/>
-    <col min="4870" max="5120" width="11.83203125" style="11" customWidth="1"/>
-    <col min="5121" max="5121" width="35" style="11" customWidth="1"/>
-    <col min="5122" max="5122" width="26" style="11" customWidth="1"/>
-    <col min="5123" max="5123" width="25.5" style="11" customWidth="1"/>
-    <col min="5124" max="5124" width="29.5" style="11" customWidth="1"/>
-    <col min="5125" max="5125" width="31.33203125" style="11" customWidth="1"/>
-    <col min="5126" max="5376" width="11.83203125" style="11" customWidth="1"/>
-    <col min="5377" max="5377" width="35" style="11" customWidth="1"/>
-    <col min="5378" max="5378" width="26" style="11" customWidth="1"/>
-    <col min="5379" max="5379" width="25.5" style="11" customWidth="1"/>
-    <col min="5380" max="5380" width="29.5" style="11" customWidth="1"/>
-    <col min="5381" max="5381" width="31.33203125" style="11" customWidth="1"/>
-    <col min="5382" max="5632" width="11.83203125" style="11" customWidth="1"/>
-    <col min="5633" max="5633" width="35" style="11" customWidth="1"/>
-    <col min="5634" max="5634" width="26" style="11" customWidth="1"/>
-    <col min="5635" max="5635" width="25.5" style="11" customWidth="1"/>
-    <col min="5636" max="5636" width="29.5" style="11" customWidth="1"/>
-    <col min="5637" max="5637" width="31.33203125" style="11" customWidth="1"/>
-    <col min="5638" max="5888" width="11.83203125" style="11" customWidth="1"/>
-    <col min="5889" max="5889" width="35" style="11" customWidth="1"/>
-    <col min="5890" max="5890" width="26" style="11" customWidth="1"/>
-    <col min="5891" max="5891" width="25.5" style="11" customWidth="1"/>
-    <col min="5892" max="5892" width="29.5" style="11" customWidth="1"/>
-    <col min="5893" max="5893" width="31.33203125" style="11" customWidth="1"/>
-    <col min="5894" max="6144" width="11.83203125" style="11" customWidth="1"/>
-    <col min="6145" max="6145" width="35" style="11" customWidth="1"/>
-    <col min="6146" max="6146" width="26" style="11" customWidth="1"/>
-    <col min="6147" max="6147" width="25.5" style="11" customWidth="1"/>
-    <col min="6148" max="6148" width="29.5" style="11" customWidth="1"/>
-    <col min="6149" max="6149" width="31.33203125" style="11" customWidth="1"/>
-    <col min="6150" max="6400" width="11.83203125" style="11" customWidth="1"/>
-    <col min="6401" max="6401" width="35" style="11" customWidth="1"/>
-    <col min="6402" max="6402" width="26" style="11" customWidth="1"/>
-    <col min="6403" max="6403" width="25.5" style="11" customWidth="1"/>
-    <col min="6404" max="6404" width="29.5" style="11" customWidth="1"/>
-    <col min="6405" max="6405" width="31.33203125" style="11" customWidth="1"/>
-    <col min="6406" max="6656" width="11.83203125" style="11" customWidth="1"/>
-    <col min="6657" max="6657" width="35" style="11" customWidth="1"/>
-    <col min="6658" max="6658" width="26" style="11" customWidth="1"/>
-    <col min="6659" max="6659" width="25.5" style="11" customWidth="1"/>
-    <col min="6660" max="6660" width="29.5" style="11" customWidth="1"/>
-    <col min="6661" max="6661" width="31.33203125" style="11" customWidth="1"/>
-    <col min="6662" max="6912" width="11.83203125" style="11" customWidth="1"/>
-    <col min="6913" max="6913" width="35" style="11" customWidth="1"/>
-    <col min="6914" max="6914" width="26" style="11" customWidth="1"/>
-    <col min="6915" max="6915" width="25.5" style="11" customWidth="1"/>
-    <col min="6916" max="6916" width="29.5" style="11" customWidth="1"/>
-    <col min="6917" max="6917" width="31.33203125" style="11" customWidth="1"/>
-    <col min="6918" max="7168" width="11.83203125" style="11" customWidth="1"/>
-    <col min="7169" max="7169" width="35" style="11" customWidth="1"/>
-    <col min="7170" max="7170" width="26" style="11" customWidth="1"/>
-    <col min="7171" max="7171" width="25.5" style="11" customWidth="1"/>
-    <col min="7172" max="7172" width="29.5" style="11" customWidth="1"/>
-    <col min="7173" max="7173" width="31.33203125" style="11" customWidth="1"/>
-    <col min="7174" max="7424" width="11.83203125" style="11" customWidth="1"/>
-    <col min="7425" max="7425" width="35" style="11" customWidth="1"/>
-    <col min="7426" max="7426" width="26" style="11" customWidth="1"/>
-    <col min="7427" max="7427" width="25.5" style="11" customWidth="1"/>
-    <col min="7428" max="7428" width="29.5" style="11" customWidth="1"/>
-    <col min="7429" max="7429" width="31.33203125" style="11" customWidth="1"/>
-    <col min="7430" max="7680" width="11.83203125" style="11" customWidth="1"/>
-    <col min="7681" max="7681" width="35" style="11" customWidth="1"/>
-    <col min="7682" max="7682" width="26" style="11" customWidth="1"/>
-    <col min="7683" max="7683" width="25.5" style="11" customWidth="1"/>
-    <col min="7684" max="7684" width="29.5" style="11" customWidth="1"/>
-    <col min="7685" max="7685" width="31.33203125" style="11" customWidth="1"/>
-    <col min="7686" max="7936" width="11.83203125" style="11" customWidth="1"/>
-    <col min="7937" max="7937" width="35" style="11" customWidth="1"/>
-    <col min="7938" max="7938" width="26" style="11" customWidth="1"/>
-    <col min="7939" max="7939" width="25.5" style="11" customWidth="1"/>
-    <col min="7940" max="7940" width="29.5" style="11" customWidth="1"/>
-    <col min="7941" max="7941" width="31.33203125" style="11" customWidth="1"/>
-    <col min="7942" max="8192" width="11.83203125" style="11" customWidth="1"/>
-    <col min="8193" max="8193" width="35" style="11" customWidth="1"/>
-    <col min="8194" max="8194" width="26" style="11" customWidth="1"/>
-    <col min="8195" max="8195" width="25.5" style="11" customWidth="1"/>
-    <col min="8196" max="8196" width="29.5" style="11" customWidth="1"/>
-    <col min="8197" max="8197" width="31.33203125" style="11" customWidth="1"/>
-    <col min="8198" max="8448" width="11.83203125" style="11" customWidth="1"/>
-    <col min="8449" max="8449" width="35" style="11" customWidth="1"/>
-    <col min="8450" max="8450" width="26" style="11" customWidth="1"/>
-    <col min="8451" max="8451" width="25.5" style="11" customWidth="1"/>
-    <col min="8452" max="8452" width="29.5" style="11" customWidth="1"/>
-    <col min="8453" max="8453" width="31.33203125" style="11" customWidth="1"/>
-    <col min="8454" max="8704" width="11.83203125" style="11" customWidth="1"/>
-    <col min="8705" max="8705" width="35" style="11" customWidth="1"/>
-    <col min="8706" max="8706" width="26" style="11" customWidth="1"/>
-    <col min="8707" max="8707" width="25.5" style="11" customWidth="1"/>
-    <col min="8708" max="8708" width="29.5" style="11" customWidth="1"/>
-    <col min="8709" max="8709" width="31.33203125" style="11" customWidth="1"/>
-    <col min="8710" max="8960" width="11.83203125" style="11" customWidth="1"/>
-    <col min="8961" max="8961" width="35" style="11" customWidth="1"/>
-    <col min="8962" max="8962" width="26" style="11" customWidth="1"/>
-    <col min="8963" max="8963" width="25.5" style="11" customWidth="1"/>
-    <col min="8964" max="8964" width="29.5" style="11" customWidth="1"/>
-    <col min="8965" max="8965" width="31.33203125" style="11" customWidth="1"/>
-    <col min="8966" max="9216" width="11.83203125" style="11" customWidth="1"/>
-    <col min="9217" max="9217" width="35" style="11" customWidth="1"/>
-    <col min="9218" max="9218" width="26" style="11" customWidth="1"/>
-    <col min="9219" max="9219" width="25.5" style="11" customWidth="1"/>
-    <col min="9220" max="9220" width="29.5" style="11" customWidth="1"/>
-    <col min="9221" max="9221" width="31.33203125" style="11" customWidth="1"/>
-    <col min="9222" max="9472" width="11.83203125" style="11" customWidth="1"/>
-    <col min="9473" max="9473" width="35" style="11" customWidth="1"/>
-    <col min="9474" max="9474" width="26" style="11" customWidth="1"/>
-    <col min="9475" max="9475" width="25.5" style="11" customWidth="1"/>
-    <col min="9476" max="9476" width="29.5" style="11" customWidth="1"/>
-    <col min="9477" max="9477" width="31.33203125" style="11" customWidth="1"/>
-    <col min="9478" max="9728" width="11.83203125" style="11" customWidth="1"/>
-    <col min="9729" max="9729" width="35" style="11" customWidth="1"/>
-    <col min="9730" max="9730" width="26" style="11" customWidth="1"/>
-    <col min="9731" max="9731" width="25.5" style="11" customWidth="1"/>
-    <col min="9732" max="9732" width="29.5" style="11" customWidth="1"/>
-    <col min="9733" max="9733" width="31.33203125" style="11" customWidth="1"/>
-    <col min="9734" max="9984" width="11.83203125" style="11" customWidth="1"/>
-    <col min="9985" max="9985" width="35" style="11" customWidth="1"/>
-    <col min="9986" max="9986" width="26" style="11" customWidth="1"/>
-    <col min="9987" max="9987" width="25.5" style="11" customWidth="1"/>
-    <col min="9988" max="9988" width="29.5" style="11" customWidth="1"/>
-    <col min="9989" max="9989" width="31.33203125" style="11" customWidth="1"/>
-    <col min="9990" max="10240" width="11.83203125" style="11" customWidth="1"/>
-    <col min="10241" max="10241" width="35" style="11" customWidth="1"/>
-    <col min="10242" max="10242" width="26" style="11" customWidth="1"/>
-    <col min="10243" max="10243" width="25.5" style="11" customWidth="1"/>
-    <col min="10244" max="10244" width="29.5" style="11" customWidth="1"/>
-    <col min="10245" max="10245" width="31.33203125" style="11" customWidth="1"/>
-    <col min="10246" max="10496" width="11.83203125" style="11" customWidth="1"/>
-    <col min="10497" max="10497" width="35" style="11" customWidth="1"/>
-    <col min="10498" max="10498" width="26" style="11" customWidth="1"/>
-    <col min="10499" max="10499" width="25.5" style="11" customWidth="1"/>
-    <col min="10500" max="10500" width="29.5" style="11" customWidth="1"/>
-    <col min="10501" max="10501" width="31.33203125" style="11" customWidth="1"/>
-    <col min="10502" max="10752" width="11.83203125" style="11" customWidth="1"/>
-    <col min="10753" max="10753" width="35" style="11" customWidth="1"/>
-    <col min="10754" max="10754" width="26" style="11" customWidth="1"/>
-    <col min="10755" max="10755" width="25.5" style="11" customWidth="1"/>
-    <col min="10756" max="10756" width="29.5" style="11" customWidth="1"/>
-    <col min="10757" max="10757" width="31.33203125" style="11" customWidth="1"/>
-    <col min="10758" max="11008" width="11.83203125" style="11" customWidth="1"/>
-    <col min="11009" max="11009" width="35" style="11" customWidth="1"/>
-    <col min="11010" max="11010" width="26" style="11" customWidth="1"/>
-    <col min="11011" max="11011" width="25.5" style="11" customWidth="1"/>
-    <col min="11012" max="11012" width="29.5" style="11" customWidth="1"/>
-    <col min="11013" max="11013" width="31.33203125" style="11" customWidth="1"/>
-    <col min="11014" max="11264" width="11.83203125" style="11" customWidth="1"/>
-    <col min="11265" max="11265" width="35" style="11" customWidth="1"/>
-    <col min="11266" max="11266" width="26" style="11" customWidth="1"/>
-    <col min="11267" max="11267" width="25.5" style="11" customWidth="1"/>
-    <col min="11268" max="11268" width="29.5" style="11" customWidth="1"/>
-    <col min="11269" max="11269" width="31.33203125" style="11" customWidth="1"/>
-    <col min="11270" max="11520" width="11.83203125" style="11" customWidth="1"/>
-    <col min="11521" max="11521" width="35" style="11" customWidth="1"/>
-    <col min="11522" max="11522" width="26" style="11" customWidth="1"/>
-    <col min="11523" max="11523" width="25.5" style="11" customWidth="1"/>
-    <col min="11524" max="11524" width="29.5" style="11" customWidth="1"/>
-    <col min="11525" max="11525" width="31.33203125" style="11" customWidth="1"/>
-    <col min="11526" max="11776" width="11.83203125" style="11" customWidth="1"/>
-    <col min="11777" max="11777" width="35" style="11" customWidth="1"/>
-    <col min="11778" max="11778" width="26" style="11" customWidth="1"/>
-    <col min="11779" max="11779" width="25.5" style="11" customWidth="1"/>
-    <col min="11780" max="11780" width="29.5" style="11" customWidth="1"/>
-    <col min="11781" max="11781" width="31.33203125" style="11" customWidth="1"/>
-    <col min="11782" max="12032" width="11.83203125" style="11" customWidth="1"/>
-    <col min="12033" max="12033" width="35" style="11" customWidth="1"/>
-    <col min="12034" max="12034" width="26" style="11" customWidth="1"/>
-    <col min="12035" max="12035" width="25.5" style="11" customWidth="1"/>
-    <col min="12036" max="12036" width="29.5" style="11" customWidth="1"/>
-    <col min="12037" max="12037" width="31.33203125" style="11" customWidth="1"/>
-    <col min="12038" max="12288" width="11.83203125" style="11" customWidth="1"/>
-    <col min="12289" max="12289" width="35" style="11" customWidth="1"/>
-    <col min="12290" max="12290" width="26" style="11" customWidth="1"/>
-    <col min="12291" max="12291" width="25.5" style="11" customWidth="1"/>
-    <col min="12292" max="12292" width="29.5" style="11" customWidth="1"/>
-    <col min="12293" max="12293" width="31.33203125" style="11" customWidth="1"/>
-    <col min="12294" max="12544" width="11.83203125" style="11" customWidth="1"/>
-    <col min="12545" max="12545" width="35" style="11" customWidth="1"/>
-    <col min="12546" max="12546" width="26" style="11" customWidth="1"/>
-    <col min="12547" max="12547" width="25.5" style="11" customWidth="1"/>
-    <col min="12548" max="12548" width="29.5" style="11" customWidth="1"/>
-    <col min="12549" max="12549" width="31.33203125" style="11" customWidth="1"/>
-    <col min="12550" max="12800" width="11.83203125" style="11" customWidth="1"/>
-    <col min="12801" max="12801" width="35" style="11" customWidth="1"/>
-    <col min="12802" max="12802" width="26" style="11" customWidth="1"/>
-    <col min="12803" max="12803" width="25.5" style="11" customWidth="1"/>
-    <col min="12804" max="12804" width="29.5" style="11" customWidth="1"/>
-    <col min="12805" max="12805" width="31.33203125" style="11" customWidth="1"/>
-    <col min="12806" max="13056" width="11.83203125" style="11" customWidth="1"/>
-    <col min="13057" max="13057" width="35" style="11" customWidth="1"/>
-    <col min="13058" max="13058" width="26" style="11" customWidth="1"/>
-    <col min="13059" max="13059" width="25.5" style="11" customWidth="1"/>
-    <col min="13060" max="13060" width="29.5" style="11" customWidth="1"/>
-    <col min="13061" max="13061" width="31.33203125" style="11" customWidth="1"/>
-    <col min="13062" max="13312" width="11.83203125" style="11" customWidth="1"/>
-    <col min="13313" max="13313" width="35" style="11" customWidth="1"/>
-    <col min="13314" max="13314" width="26" style="11" customWidth="1"/>
-    <col min="13315" max="13315" width="25.5" style="11" customWidth="1"/>
-    <col min="13316" max="13316" width="29.5" style="11" customWidth="1"/>
-    <col min="13317" max="13317" width="31.33203125" style="11" customWidth="1"/>
-    <col min="13318" max="13568" width="11.83203125" style="11" customWidth="1"/>
-    <col min="13569" max="13569" width="35" style="11" customWidth="1"/>
-    <col min="13570" max="13570" width="26" style="11" customWidth="1"/>
-    <col min="13571" max="13571" width="25.5" style="11" customWidth="1"/>
-    <col min="13572" max="13572" width="29.5" style="11" customWidth="1"/>
-    <col min="13573" max="13573" width="31.33203125" style="11" customWidth="1"/>
-    <col min="13574" max="13824" width="11.83203125" style="11" customWidth="1"/>
-    <col min="13825" max="13825" width="35" style="11" customWidth="1"/>
-    <col min="13826" max="13826" width="26" style="11" customWidth="1"/>
-    <col min="13827" max="13827" width="25.5" style="11" customWidth="1"/>
-    <col min="13828" max="13828" width="29.5" style="11" customWidth="1"/>
-    <col min="13829" max="13829" width="31.33203125" style="11" customWidth="1"/>
-    <col min="13830" max="14080" width="11.83203125" style="11" customWidth="1"/>
-    <col min="14081" max="14081" width="35" style="11" customWidth="1"/>
-    <col min="14082" max="14082" width="26" style="11" customWidth="1"/>
-    <col min="14083" max="14083" width="25.5" style="11" customWidth="1"/>
-    <col min="14084" max="14084" width="29.5" style="11" customWidth="1"/>
-    <col min="14085" max="14085" width="31.33203125" style="11" customWidth="1"/>
-    <col min="14086" max="14336" width="11.83203125" style="11" customWidth="1"/>
-    <col min="14337" max="14337" width="35" style="11" customWidth="1"/>
-    <col min="14338" max="14338" width="26" style="11" customWidth="1"/>
-    <col min="14339" max="14339" width="25.5" style="11" customWidth="1"/>
-    <col min="14340" max="14340" width="29.5" style="11" customWidth="1"/>
-    <col min="14341" max="14341" width="31.33203125" style="11" customWidth="1"/>
-    <col min="14342" max="14592" width="11.83203125" style="11" customWidth="1"/>
-    <col min="14593" max="14593" width="35" style="11" customWidth="1"/>
-    <col min="14594" max="14594" width="26" style="11" customWidth="1"/>
-    <col min="14595" max="14595" width="25.5" style="11" customWidth="1"/>
-    <col min="14596" max="14596" width="29.5" style="11" customWidth="1"/>
-    <col min="14597" max="14597" width="31.33203125" style="11" customWidth="1"/>
-    <col min="14598" max="14848" width="11.83203125" style="11" customWidth="1"/>
-    <col min="14849" max="14849" width="35" style="11" customWidth="1"/>
-    <col min="14850" max="14850" width="26" style="11" customWidth="1"/>
-    <col min="14851" max="14851" width="25.5" style="11" customWidth="1"/>
-    <col min="14852" max="14852" width="29.5" style="11" customWidth="1"/>
-    <col min="14853" max="14853" width="31.33203125" style="11" customWidth="1"/>
-    <col min="14854" max="15104" width="11.83203125" style="11" customWidth="1"/>
-    <col min="15105" max="15105" width="35" style="11" customWidth="1"/>
-    <col min="15106" max="15106" width="26" style="11" customWidth="1"/>
-    <col min="15107" max="15107" width="25.5" style="11" customWidth="1"/>
-    <col min="15108" max="15108" width="29.5" style="11" customWidth="1"/>
-    <col min="15109" max="15109" width="31.33203125" style="11" customWidth="1"/>
-    <col min="15110" max="15360" width="11.83203125" style="11" customWidth="1"/>
-    <col min="15361" max="15361" width="35" style="11" customWidth="1"/>
-    <col min="15362" max="15362" width="26" style="11" customWidth="1"/>
-    <col min="15363" max="15363" width="25.5" style="11" customWidth="1"/>
-    <col min="15364" max="15364" width="29.5" style="11" customWidth="1"/>
-    <col min="15365" max="15365" width="31.33203125" style="11" customWidth="1"/>
-    <col min="15366" max="15616" width="11.83203125" style="11" customWidth="1"/>
-    <col min="15617" max="15617" width="35" style="11" customWidth="1"/>
-    <col min="15618" max="15618" width="26" style="11" customWidth="1"/>
-    <col min="15619" max="15619" width="25.5" style="11" customWidth="1"/>
-    <col min="15620" max="15620" width="29.5" style="11" customWidth="1"/>
-    <col min="15621" max="15621" width="31.33203125" style="11" customWidth="1"/>
-    <col min="15622" max="15872" width="11.83203125" style="11" customWidth="1"/>
-    <col min="15873" max="15873" width="35" style="11" customWidth="1"/>
-    <col min="15874" max="15874" width="26" style="11" customWidth="1"/>
-    <col min="15875" max="15875" width="25.5" style="11" customWidth="1"/>
-    <col min="15876" max="15876" width="29.5" style="11" customWidth="1"/>
-    <col min="15877" max="15877" width="31.33203125" style="11" customWidth="1"/>
-    <col min="15878" max="16128" width="11.83203125" style="11" customWidth="1"/>
-    <col min="16129" max="16129" width="35" style="11" customWidth="1"/>
-    <col min="16130" max="16130" width="26" style="11" customWidth="1"/>
-    <col min="16131" max="16131" width="25.5" style="11" customWidth="1"/>
-    <col min="16132" max="16132" width="29.5" style="11" customWidth="1"/>
-    <col min="16133" max="16133" width="31.33203125" style="11" customWidth="1"/>
-    <col min="16134" max="16384" width="11.83203125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="35" style="23" customWidth="1"/>
+    <col min="2" max="2" width="26" style="24" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="24" customWidth="1"/>
+    <col min="4" max="4" width="29.5" style="24" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" style="24" customWidth="1"/>
+    <col min="6" max="256" width="11.83203125" style="7" customWidth="1"/>
+    <col min="257" max="257" width="35" style="7" customWidth="1"/>
+    <col min="258" max="258" width="26" style="7" customWidth="1"/>
+    <col min="259" max="259" width="25.5" style="7" customWidth="1"/>
+    <col min="260" max="260" width="29.5" style="7" customWidth="1"/>
+    <col min="261" max="261" width="31.33203125" style="7" customWidth="1"/>
+    <col min="262" max="512" width="11.83203125" style="7" customWidth="1"/>
+    <col min="513" max="513" width="35" style="7" customWidth="1"/>
+    <col min="514" max="514" width="26" style="7" customWidth="1"/>
+    <col min="515" max="515" width="25.5" style="7" customWidth="1"/>
+    <col min="516" max="516" width="29.5" style="7" customWidth="1"/>
+    <col min="517" max="517" width="31.33203125" style="7" customWidth="1"/>
+    <col min="518" max="768" width="11.83203125" style="7" customWidth="1"/>
+    <col min="769" max="769" width="35" style="7" customWidth="1"/>
+    <col min="770" max="770" width="26" style="7" customWidth="1"/>
+    <col min="771" max="771" width="25.5" style="7" customWidth="1"/>
+    <col min="772" max="772" width="29.5" style="7" customWidth="1"/>
+    <col min="773" max="773" width="31.33203125" style="7" customWidth="1"/>
+    <col min="774" max="1024" width="11.83203125" style="7" customWidth="1"/>
+    <col min="1025" max="1025" width="35" style="7" customWidth="1"/>
+    <col min="1026" max="1026" width="26" style="7" customWidth="1"/>
+    <col min="1027" max="1027" width="25.5" style="7" customWidth="1"/>
+    <col min="1028" max="1028" width="29.5" style="7" customWidth="1"/>
+    <col min="1029" max="1029" width="31.33203125" style="7" customWidth="1"/>
+    <col min="1030" max="1280" width="11.83203125" style="7" customWidth="1"/>
+    <col min="1281" max="1281" width="35" style="7" customWidth="1"/>
+    <col min="1282" max="1282" width="26" style="7" customWidth="1"/>
+    <col min="1283" max="1283" width="25.5" style="7" customWidth="1"/>
+    <col min="1284" max="1284" width="29.5" style="7" customWidth="1"/>
+    <col min="1285" max="1285" width="31.33203125" style="7" customWidth="1"/>
+    <col min="1286" max="1536" width="11.83203125" style="7" customWidth="1"/>
+    <col min="1537" max="1537" width="35" style="7" customWidth="1"/>
+    <col min="1538" max="1538" width="26" style="7" customWidth="1"/>
+    <col min="1539" max="1539" width="25.5" style="7" customWidth="1"/>
+    <col min="1540" max="1540" width="29.5" style="7" customWidth="1"/>
+    <col min="1541" max="1541" width="31.33203125" style="7" customWidth="1"/>
+    <col min="1542" max="1792" width="11.83203125" style="7" customWidth="1"/>
+    <col min="1793" max="1793" width="35" style="7" customWidth="1"/>
+    <col min="1794" max="1794" width="26" style="7" customWidth="1"/>
+    <col min="1795" max="1795" width="25.5" style="7" customWidth="1"/>
+    <col min="1796" max="1796" width="29.5" style="7" customWidth="1"/>
+    <col min="1797" max="1797" width="31.33203125" style="7" customWidth="1"/>
+    <col min="1798" max="2048" width="11.83203125" style="7" customWidth="1"/>
+    <col min="2049" max="2049" width="35" style="7" customWidth="1"/>
+    <col min="2050" max="2050" width="26" style="7" customWidth="1"/>
+    <col min="2051" max="2051" width="25.5" style="7" customWidth="1"/>
+    <col min="2052" max="2052" width="29.5" style="7" customWidth="1"/>
+    <col min="2053" max="2053" width="31.33203125" style="7" customWidth="1"/>
+    <col min="2054" max="2304" width="11.83203125" style="7" customWidth="1"/>
+    <col min="2305" max="2305" width="35" style="7" customWidth="1"/>
+    <col min="2306" max="2306" width="26" style="7" customWidth="1"/>
+    <col min="2307" max="2307" width="25.5" style="7" customWidth="1"/>
+    <col min="2308" max="2308" width="29.5" style="7" customWidth="1"/>
+    <col min="2309" max="2309" width="31.33203125" style="7" customWidth="1"/>
+    <col min="2310" max="2560" width="11.83203125" style="7" customWidth="1"/>
+    <col min="2561" max="2561" width="35" style="7" customWidth="1"/>
+    <col min="2562" max="2562" width="26" style="7" customWidth="1"/>
+    <col min="2563" max="2563" width="25.5" style="7" customWidth="1"/>
+    <col min="2564" max="2564" width="29.5" style="7" customWidth="1"/>
+    <col min="2565" max="2565" width="31.33203125" style="7" customWidth="1"/>
+    <col min="2566" max="2816" width="11.83203125" style="7" customWidth="1"/>
+    <col min="2817" max="2817" width="35" style="7" customWidth="1"/>
+    <col min="2818" max="2818" width="26" style="7" customWidth="1"/>
+    <col min="2819" max="2819" width="25.5" style="7" customWidth="1"/>
+    <col min="2820" max="2820" width="29.5" style="7" customWidth="1"/>
+    <col min="2821" max="2821" width="31.33203125" style="7" customWidth="1"/>
+    <col min="2822" max="3072" width="11.83203125" style="7" customWidth="1"/>
+    <col min="3073" max="3073" width="35" style="7" customWidth="1"/>
+    <col min="3074" max="3074" width="26" style="7" customWidth="1"/>
+    <col min="3075" max="3075" width="25.5" style="7" customWidth="1"/>
+    <col min="3076" max="3076" width="29.5" style="7" customWidth="1"/>
+    <col min="3077" max="3077" width="31.33203125" style="7" customWidth="1"/>
+    <col min="3078" max="3328" width="11.83203125" style="7" customWidth="1"/>
+    <col min="3329" max="3329" width="35" style="7" customWidth="1"/>
+    <col min="3330" max="3330" width="26" style="7" customWidth="1"/>
+    <col min="3331" max="3331" width="25.5" style="7" customWidth="1"/>
+    <col min="3332" max="3332" width="29.5" style="7" customWidth="1"/>
+    <col min="3333" max="3333" width="31.33203125" style="7" customWidth="1"/>
+    <col min="3334" max="3584" width="11.83203125" style="7" customWidth="1"/>
+    <col min="3585" max="3585" width="35" style="7" customWidth="1"/>
+    <col min="3586" max="3586" width="26" style="7" customWidth="1"/>
+    <col min="3587" max="3587" width="25.5" style="7" customWidth="1"/>
+    <col min="3588" max="3588" width="29.5" style="7" customWidth="1"/>
+    <col min="3589" max="3589" width="31.33203125" style="7" customWidth="1"/>
+    <col min="3590" max="3840" width="11.83203125" style="7" customWidth="1"/>
+    <col min="3841" max="3841" width="35" style="7" customWidth="1"/>
+    <col min="3842" max="3842" width="26" style="7" customWidth="1"/>
+    <col min="3843" max="3843" width="25.5" style="7" customWidth="1"/>
+    <col min="3844" max="3844" width="29.5" style="7" customWidth="1"/>
+    <col min="3845" max="3845" width="31.33203125" style="7" customWidth="1"/>
+    <col min="3846" max="4096" width="11.83203125" style="7" customWidth="1"/>
+    <col min="4097" max="4097" width="35" style="7" customWidth="1"/>
+    <col min="4098" max="4098" width="26" style="7" customWidth="1"/>
+    <col min="4099" max="4099" width="25.5" style="7" customWidth="1"/>
+    <col min="4100" max="4100" width="29.5" style="7" customWidth="1"/>
+    <col min="4101" max="4101" width="31.33203125" style="7" customWidth="1"/>
+    <col min="4102" max="4352" width="11.83203125" style="7" customWidth="1"/>
+    <col min="4353" max="4353" width="35" style="7" customWidth="1"/>
+    <col min="4354" max="4354" width="26" style="7" customWidth="1"/>
+    <col min="4355" max="4355" width="25.5" style="7" customWidth="1"/>
+    <col min="4356" max="4356" width="29.5" style="7" customWidth="1"/>
+    <col min="4357" max="4357" width="31.33203125" style="7" customWidth="1"/>
+    <col min="4358" max="4608" width="11.83203125" style="7" customWidth="1"/>
+    <col min="4609" max="4609" width="35" style="7" customWidth="1"/>
+    <col min="4610" max="4610" width="26" style="7" customWidth="1"/>
+    <col min="4611" max="4611" width="25.5" style="7" customWidth="1"/>
+    <col min="4612" max="4612" width="29.5" style="7" customWidth="1"/>
+    <col min="4613" max="4613" width="31.33203125" style="7" customWidth="1"/>
+    <col min="4614" max="4864" width="11.83203125" style="7" customWidth="1"/>
+    <col min="4865" max="4865" width="35" style="7" customWidth="1"/>
+    <col min="4866" max="4866" width="26" style="7" customWidth="1"/>
+    <col min="4867" max="4867" width="25.5" style="7" customWidth="1"/>
+    <col min="4868" max="4868" width="29.5" style="7" customWidth="1"/>
+    <col min="4869" max="4869" width="31.33203125" style="7" customWidth="1"/>
+    <col min="4870" max="5120" width="11.83203125" style="7" customWidth="1"/>
+    <col min="5121" max="5121" width="35" style="7" customWidth="1"/>
+    <col min="5122" max="5122" width="26" style="7" customWidth="1"/>
+    <col min="5123" max="5123" width="25.5" style="7" customWidth="1"/>
+    <col min="5124" max="5124" width="29.5" style="7" customWidth="1"/>
+    <col min="5125" max="5125" width="31.33203125" style="7" customWidth="1"/>
+    <col min="5126" max="5376" width="11.83203125" style="7" customWidth="1"/>
+    <col min="5377" max="5377" width="35" style="7" customWidth="1"/>
+    <col min="5378" max="5378" width="26" style="7" customWidth="1"/>
+    <col min="5379" max="5379" width="25.5" style="7" customWidth="1"/>
+    <col min="5380" max="5380" width="29.5" style="7" customWidth="1"/>
+    <col min="5381" max="5381" width="31.33203125" style="7" customWidth="1"/>
+    <col min="5382" max="5632" width="11.83203125" style="7" customWidth="1"/>
+    <col min="5633" max="5633" width="35" style="7" customWidth="1"/>
+    <col min="5634" max="5634" width="26" style="7" customWidth="1"/>
+    <col min="5635" max="5635" width="25.5" style="7" customWidth="1"/>
+    <col min="5636" max="5636" width="29.5" style="7" customWidth="1"/>
+    <col min="5637" max="5637" width="31.33203125" style="7" customWidth="1"/>
+    <col min="5638" max="5888" width="11.83203125" style="7" customWidth="1"/>
+    <col min="5889" max="5889" width="35" style="7" customWidth="1"/>
+    <col min="5890" max="5890" width="26" style="7" customWidth="1"/>
+    <col min="5891" max="5891" width="25.5" style="7" customWidth="1"/>
+    <col min="5892" max="5892" width="29.5" style="7" customWidth="1"/>
+    <col min="5893" max="5893" width="31.33203125" style="7" customWidth="1"/>
+    <col min="5894" max="6144" width="11.83203125" style="7" customWidth="1"/>
+    <col min="6145" max="6145" width="35" style="7" customWidth="1"/>
+    <col min="6146" max="6146" width="26" style="7" customWidth="1"/>
+    <col min="6147" max="6147" width="25.5" style="7" customWidth="1"/>
+    <col min="6148" max="6148" width="29.5" style="7" customWidth="1"/>
+    <col min="6149" max="6149" width="31.33203125" style="7" customWidth="1"/>
+    <col min="6150" max="6400" width="11.83203125" style="7" customWidth="1"/>
+    <col min="6401" max="6401" width="35" style="7" customWidth="1"/>
+    <col min="6402" max="6402" width="26" style="7" customWidth="1"/>
+    <col min="6403" max="6403" width="25.5" style="7" customWidth="1"/>
+    <col min="6404" max="6404" width="29.5" style="7" customWidth="1"/>
+    <col min="6405" max="6405" width="31.33203125" style="7" customWidth="1"/>
+    <col min="6406" max="6656" width="11.83203125" style="7" customWidth="1"/>
+    <col min="6657" max="6657" width="35" style="7" customWidth="1"/>
+    <col min="6658" max="6658" width="26" style="7" customWidth="1"/>
+    <col min="6659" max="6659" width="25.5" style="7" customWidth="1"/>
+    <col min="6660" max="6660" width="29.5" style="7" customWidth="1"/>
+    <col min="6661" max="6661" width="31.33203125" style="7" customWidth="1"/>
+    <col min="6662" max="6912" width="11.83203125" style="7" customWidth="1"/>
+    <col min="6913" max="6913" width="35" style="7" customWidth="1"/>
+    <col min="6914" max="6914" width="26" style="7" customWidth="1"/>
+    <col min="6915" max="6915" width="25.5" style="7" customWidth="1"/>
+    <col min="6916" max="6916" width="29.5" style="7" customWidth="1"/>
+    <col min="6917" max="6917" width="31.33203125" style="7" customWidth="1"/>
+    <col min="6918" max="7168" width="11.83203125" style="7" customWidth="1"/>
+    <col min="7169" max="7169" width="35" style="7" customWidth="1"/>
+    <col min="7170" max="7170" width="26" style="7" customWidth="1"/>
+    <col min="7171" max="7171" width="25.5" style="7" customWidth="1"/>
+    <col min="7172" max="7172" width="29.5" style="7" customWidth="1"/>
+    <col min="7173" max="7173" width="31.33203125" style="7" customWidth="1"/>
+    <col min="7174" max="7424" width="11.83203125" style="7" customWidth="1"/>
+    <col min="7425" max="7425" width="35" style="7" customWidth="1"/>
+    <col min="7426" max="7426" width="26" style="7" customWidth="1"/>
+    <col min="7427" max="7427" width="25.5" style="7" customWidth="1"/>
+    <col min="7428" max="7428" width="29.5" style="7" customWidth="1"/>
+    <col min="7429" max="7429" width="31.33203125" style="7" customWidth="1"/>
+    <col min="7430" max="7680" width="11.83203125" style="7" customWidth="1"/>
+    <col min="7681" max="7681" width="35" style="7" customWidth="1"/>
+    <col min="7682" max="7682" width="26" style="7" customWidth="1"/>
+    <col min="7683" max="7683" width="25.5" style="7" customWidth="1"/>
+    <col min="7684" max="7684" width="29.5" style="7" customWidth="1"/>
+    <col min="7685" max="7685" width="31.33203125" style="7" customWidth="1"/>
+    <col min="7686" max="7936" width="11.83203125" style="7" customWidth="1"/>
+    <col min="7937" max="7937" width="35" style="7" customWidth="1"/>
+    <col min="7938" max="7938" width="26" style="7" customWidth="1"/>
+    <col min="7939" max="7939" width="25.5" style="7" customWidth="1"/>
+    <col min="7940" max="7940" width="29.5" style="7" customWidth="1"/>
+    <col min="7941" max="7941" width="31.33203125" style="7" customWidth="1"/>
+    <col min="7942" max="8192" width="11.83203125" style="7" customWidth="1"/>
+    <col min="8193" max="8193" width="35" style="7" customWidth="1"/>
+    <col min="8194" max="8194" width="26" style="7" customWidth="1"/>
+    <col min="8195" max="8195" width="25.5" style="7" customWidth="1"/>
+    <col min="8196" max="8196" width="29.5" style="7" customWidth="1"/>
+    <col min="8197" max="8197" width="31.33203125" style="7" customWidth="1"/>
+    <col min="8198" max="8448" width="11.83203125" style="7" customWidth="1"/>
+    <col min="8449" max="8449" width="35" style="7" customWidth="1"/>
+    <col min="8450" max="8450" width="26" style="7" customWidth="1"/>
+    <col min="8451" max="8451" width="25.5" style="7" customWidth="1"/>
+    <col min="8452" max="8452" width="29.5" style="7" customWidth="1"/>
+    <col min="8453" max="8453" width="31.33203125" style="7" customWidth="1"/>
+    <col min="8454" max="8704" width="11.83203125" style="7" customWidth="1"/>
+    <col min="8705" max="8705" width="35" style="7" customWidth="1"/>
+    <col min="8706" max="8706" width="26" style="7" customWidth="1"/>
+    <col min="8707" max="8707" width="25.5" style="7" customWidth="1"/>
+    <col min="8708" max="8708" width="29.5" style="7" customWidth="1"/>
+    <col min="8709" max="8709" width="31.33203125" style="7" customWidth="1"/>
+    <col min="8710" max="8960" width="11.83203125" style="7" customWidth="1"/>
+    <col min="8961" max="8961" width="35" style="7" customWidth="1"/>
+    <col min="8962" max="8962" width="26" style="7" customWidth="1"/>
+    <col min="8963" max="8963" width="25.5" style="7" customWidth="1"/>
+    <col min="8964" max="8964" width="29.5" style="7" customWidth="1"/>
+    <col min="8965" max="8965" width="31.33203125" style="7" customWidth="1"/>
+    <col min="8966" max="9216" width="11.83203125" style="7" customWidth="1"/>
+    <col min="9217" max="9217" width="35" style="7" customWidth="1"/>
+    <col min="9218" max="9218" width="26" style="7" customWidth="1"/>
+    <col min="9219" max="9219" width="25.5" style="7" customWidth="1"/>
+    <col min="9220" max="9220" width="29.5" style="7" customWidth="1"/>
+    <col min="9221" max="9221" width="31.33203125" style="7" customWidth="1"/>
+    <col min="9222" max="9472" width="11.83203125" style="7" customWidth="1"/>
+    <col min="9473" max="9473" width="35" style="7" customWidth="1"/>
+    <col min="9474" max="9474" width="26" style="7" customWidth="1"/>
+    <col min="9475" max="9475" width="25.5" style="7" customWidth="1"/>
+    <col min="9476" max="9476" width="29.5" style="7" customWidth="1"/>
+    <col min="9477" max="9477" width="31.33203125" style="7" customWidth="1"/>
+    <col min="9478" max="9728" width="11.83203125" style="7" customWidth="1"/>
+    <col min="9729" max="9729" width="35" style="7" customWidth="1"/>
+    <col min="9730" max="9730" width="26" style="7" customWidth="1"/>
+    <col min="9731" max="9731" width="25.5" style="7" customWidth="1"/>
+    <col min="9732" max="9732" width="29.5" style="7" customWidth="1"/>
+    <col min="9733" max="9733" width="31.33203125" style="7" customWidth="1"/>
+    <col min="9734" max="9984" width="11.83203125" style="7" customWidth="1"/>
+    <col min="9985" max="9985" width="35" style="7" customWidth="1"/>
+    <col min="9986" max="9986" width="26" style="7" customWidth="1"/>
+    <col min="9987" max="9987" width="25.5" style="7" customWidth="1"/>
+    <col min="9988" max="9988" width="29.5" style="7" customWidth="1"/>
+    <col min="9989" max="9989" width="31.33203125" style="7" customWidth="1"/>
+    <col min="9990" max="10240" width="11.83203125" style="7" customWidth="1"/>
+    <col min="10241" max="10241" width="35" style="7" customWidth="1"/>
+    <col min="10242" max="10242" width="26" style="7" customWidth="1"/>
+    <col min="10243" max="10243" width="25.5" style="7" customWidth="1"/>
+    <col min="10244" max="10244" width="29.5" style="7" customWidth="1"/>
+    <col min="10245" max="10245" width="31.33203125" style="7" customWidth="1"/>
+    <col min="10246" max="10496" width="11.83203125" style="7" customWidth="1"/>
+    <col min="10497" max="10497" width="35" style="7" customWidth="1"/>
+    <col min="10498" max="10498" width="26" style="7" customWidth="1"/>
+    <col min="10499" max="10499" width="25.5" style="7" customWidth="1"/>
+    <col min="10500" max="10500" width="29.5" style="7" customWidth="1"/>
+    <col min="10501" max="10501" width="31.33203125" style="7" customWidth="1"/>
+    <col min="10502" max="10752" width="11.83203125" style="7" customWidth="1"/>
+    <col min="10753" max="10753" width="35" style="7" customWidth="1"/>
+    <col min="10754" max="10754" width="26" style="7" customWidth="1"/>
+    <col min="10755" max="10755" width="25.5" style="7" customWidth="1"/>
+    <col min="10756" max="10756" width="29.5" style="7" customWidth="1"/>
+    <col min="10757" max="10757" width="31.33203125" style="7" customWidth="1"/>
+    <col min="10758" max="11008" width="11.83203125" style="7" customWidth="1"/>
+    <col min="11009" max="11009" width="35" style="7" customWidth="1"/>
+    <col min="11010" max="11010" width="26" style="7" customWidth="1"/>
+    <col min="11011" max="11011" width="25.5" style="7" customWidth="1"/>
+    <col min="11012" max="11012" width="29.5" style="7" customWidth="1"/>
+    <col min="11013" max="11013" width="31.33203125" style="7" customWidth="1"/>
+    <col min="11014" max="11264" width="11.83203125" style="7" customWidth="1"/>
+    <col min="11265" max="11265" width="35" style="7" customWidth="1"/>
+    <col min="11266" max="11266" width="26" style="7" customWidth="1"/>
+    <col min="11267" max="11267" width="25.5" style="7" customWidth="1"/>
+    <col min="11268" max="11268" width="29.5" style="7" customWidth="1"/>
+    <col min="11269" max="11269" width="31.33203125" style="7" customWidth="1"/>
+    <col min="11270" max="11520" width="11.83203125" style="7" customWidth="1"/>
+    <col min="11521" max="11521" width="35" style="7" customWidth="1"/>
+    <col min="11522" max="11522" width="26" style="7" customWidth="1"/>
+    <col min="11523" max="11523" width="25.5" style="7" customWidth="1"/>
+    <col min="11524" max="11524" width="29.5" style="7" customWidth="1"/>
+    <col min="11525" max="11525" width="31.33203125" style="7" customWidth="1"/>
+    <col min="11526" max="11776" width="11.83203125" style="7" customWidth="1"/>
+    <col min="11777" max="11777" width="35" style="7" customWidth="1"/>
+    <col min="11778" max="11778" width="26" style="7" customWidth="1"/>
+    <col min="11779" max="11779" width="25.5" style="7" customWidth="1"/>
+    <col min="11780" max="11780" width="29.5" style="7" customWidth="1"/>
+    <col min="11781" max="11781" width="31.33203125" style="7" customWidth="1"/>
+    <col min="11782" max="12032" width="11.83203125" style="7" customWidth="1"/>
+    <col min="12033" max="12033" width="35" style="7" customWidth="1"/>
+    <col min="12034" max="12034" width="26" style="7" customWidth="1"/>
+    <col min="12035" max="12035" width="25.5" style="7" customWidth="1"/>
+    <col min="12036" max="12036" width="29.5" style="7" customWidth="1"/>
+    <col min="12037" max="12037" width="31.33203125" style="7" customWidth="1"/>
+    <col min="12038" max="12288" width="11.83203125" style="7" customWidth="1"/>
+    <col min="12289" max="12289" width="35" style="7" customWidth="1"/>
+    <col min="12290" max="12290" width="26" style="7" customWidth="1"/>
+    <col min="12291" max="12291" width="25.5" style="7" customWidth="1"/>
+    <col min="12292" max="12292" width="29.5" style="7" customWidth="1"/>
+    <col min="12293" max="12293" width="31.33203125" style="7" customWidth="1"/>
+    <col min="12294" max="12544" width="11.83203125" style="7" customWidth="1"/>
+    <col min="12545" max="12545" width="35" style="7" customWidth="1"/>
+    <col min="12546" max="12546" width="26" style="7" customWidth="1"/>
+    <col min="12547" max="12547" width="25.5" style="7" customWidth="1"/>
+    <col min="12548" max="12548" width="29.5" style="7" customWidth="1"/>
+    <col min="12549" max="12549" width="31.33203125" style="7" customWidth="1"/>
+    <col min="12550" max="12800" width="11.83203125" style="7" customWidth="1"/>
+    <col min="12801" max="12801" width="35" style="7" customWidth="1"/>
+    <col min="12802" max="12802" width="26" style="7" customWidth="1"/>
+    <col min="12803" max="12803" width="25.5" style="7" customWidth="1"/>
+    <col min="12804" max="12804" width="29.5" style="7" customWidth="1"/>
+    <col min="12805" max="12805" width="31.33203125" style="7" customWidth="1"/>
+    <col min="12806" max="13056" width="11.83203125" style="7" customWidth="1"/>
+    <col min="13057" max="13057" width="35" style="7" customWidth="1"/>
+    <col min="13058" max="13058" width="26" style="7" customWidth="1"/>
+    <col min="13059" max="13059" width="25.5" style="7" customWidth="1"/>
+    <col min="13060" max="13060" width="29.5" style="7" customWidth="1"/>
+    <col min="13061" max="13061" width="31.33203125" style="7" customWidth="1"/>
+    <col min="13062" max="13312" width="11.83203125" style="7" customWidth="1"/>
+    <col min="13313" max="13313" width="35" style="7" customWidth="1"/>
+    <col min="13314" max="13314" width="26" style="7" customWidth="1"/>
+    <col min="13315" max="13315" width="25.5" style="7" customWidth="1"/>
+    <col min="13316" max="13316" width="29.5" style="7" customWidth="1"/>
+    <col min="13317" max="13317" width="31.33203125" style="7" customWidth="1"/>
+    <col min="13318" max="13568" width="11.83203125" style="7" customWidth="1"/>
+    <col min="13569" max="13569" width="35" style="7" customWidth="1"/>
+    <col min="13570" max="13570" width="26" style="7" customWidth="1"/>
+    <col min="13571" max="13571" width="25.5" style="7" customWidth="1"/>
+    <col min="13572" max="13572" width="29.5" style="7" customWidth="1"/>
+    <col min="13573" max="13573" width="31.33203125" style="7" customWidth="1"/>
+    <col min="13574" max="13824" width="11.83203125" style="7" customWidth="1"/>
+    <col min="13825" max="13825" width="35" style="7" customWidth="1"/>
+    <col min="13826" max="13826" width="26" style="7" customWidth="1"/>
+    <col min="13827" max="13827" width="25.5" style="7" customWidth="1"/>
+    <col min="13828" max="13828" width="29.5" style="7" customWidth="1"/>
+    <col min="13829" max="13829" width="31.33203125" style="7" customWidth="1"/>
+    <col min="13830" max="14080" width="11.83203125" style="7" customWidth="1"/>
+    <col min="14081" max="14081" width="35" style="7" customWidth="1"/>
+    <col min="14082" max="14082" width="26" style="7" customWidth="1"/>
+    <col min="14083" max="14083" width="25.5" style="7" customWidth="1"/>
+    <col min="14084" max="14084" width="29.5" style="7" customWidth="1"/>
+    <col min="14085" max="14085" width="31.33203125" style="7" customWidth="1"/>
+    <col min="14086" max="14336" width="11.83203125" style="7" customWidth="1"/>
+    <col min="14337" max="14337" width="35" style="7" customWidth="1"/>
+    <col min="14338" max="14338" width="26" style="7" customWidth="1"/>
+    <col min="14339" max="14339" width="25.5" style="7" customWidth="1"/>
+    <col min="14340" max="14340" width="29.5" style="7" customWidth="1"/>
+    <col min="14341" max="14341" width="31.33203125" style="7" customWidth="1"/>
+    <col min="14342" max="14592" width="11.83203125" style="7" customWidth="1"/>
+    <col min="14593" max="14593" width="35" style="7" customWidth="1"/>
+    <col min="14594" max="14594" width="26" style="7" customWidth="1"/>
+    <col min="14595" max="14595" width="25.5" style="7" customWidth="1"/>
+    <col min="14596" max="14596" width="29.5" style="7" customWidth="1"/>
+    <col min="14597" max="14597" width="31.33203125" style="7" customWidth="1"/>
+    <col min="14598" max="14848" width="11.83203125" style="7" customWidth="1"/>
+    <col min="14849" max="14849" width="35" style="7" customWidth="1"/>
+    <col min="14850" max="14850" width="26" style="7" customWidth="1"/>
+    <col min="14851" max="14851" width="25.5" style="7" customWidth="1"/>
+    <col min="14852" max="14852" width="29.5" style="7" customWidth="1"/>
+    <col min="14853" max="14853" width="31.33203125" style="7" customWidth="1"/>
+    <col min="14854" max="15104" width="11.83203125" style="7" customWidth="1"/>
+    <col min="15105" max="15105" width="35" style="7" customWidth="1"/>
+    <col min="15106" max="15106" width="26" style="7" customWidth="1"/>
+    <col min="15107" max="15107" width="25.5" style="7" customWidth="1"/>
+    <col min="15108" max="15108" width="29.5" style="7" customWidth="1"/>
+    <col min="15109" max="15109" width="31.33203125" style="7" customWidth="1"/>
+    <col min="15110" max="15360" width="11.83203125" style="7" customWidth="1"/>
+    <col min="15361" max="15361" width="35" style="7" customWidth="1"/>
+    <col min="15362" max="15362" width="26" style="7" customWidth="1"/>
+    <col min="15363" max="15363" width="25.5" style="7" customWidth="1"/>
+    <col min="15364" max="15364" width="29.5" style="7" customWidth="1"/>
+    <col min="15365" max="15365" width="31.33203125" style="7" customWidth="1"/>
+    <col min="15366" max="15616" width="11.83203125" style="7" customWidth="1"/>
+    <col min="15617" max="15617" width="35" style="7" customWidth="1"/>
+    <col min="15618" max="15618" width="26" style="7" customWidth="1"/>
+    <col min="15619" max="15619" width="25.5" style="7" customWidth="1"/>
+    <col min="15620" max="15620" width="29.5" style="7" customWidth="1"/>
+    <col min="15621" max="15621" width="31.33203125" style="7" customWidth="1"/>
+    <col min="15622" max="15872" width="11.83203125" style="7" customWidth="1"/>
+    <col min="15873" max="15873" width="35" style="7" customWidth="1"/>
+    <col min="15874" max="15874" width="26" style="7" customWidth="1"/>
+    <col min="15875" max="15875" width="25.5" style="7" customWidth="1"/>
+    <col min="15876" max="15876" width="29.5" style="7" customWidth="1"/>
+    <col min="15877" max="15877" width="31.33203125" style="7" customWidth="1"/>
+    <col min="15878" max="16128" width="11.83203125" style="7" customWidth="1"/>
+    <col min="16129" max="16129" width="35" style="7" customWidth="1"/>
+    <col min="16130" max="16130" width="26" style="7" customWidth="1"/>
+    <col min="16131" max="16131" width="25.5" style="7" customWidth="1"/>
+    <col min="16132" max="16132" width="29.5" style="7" customWidth="1"/>
+    <col min="16133" max="16133" width="31.33203125" style="7" customWidth="1"/>
+    <col min="16134" max="16384" width="11.83203125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" thickBot="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="1:5" ht="29" thickTop="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="12" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="9" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>67.357284981685723</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <v>17.021601616846862</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="11">
         <v>7.5239000366335507</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="12">
         <v>91.902786635166137</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>85.237727472578783</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="11">
         <v>0.32836943453342105</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="11">
         <v>0.89632658778486352</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>86.462423494897067</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>18.014721151565009</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <v>23.820203532706653</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="11">
         <v>25.351012271734341</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="12">
         <v>67.185936956006003</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>23.443309585698938</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="11">
         <v>10.944392945924191</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="11">
         <v>33.446598319816452</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>67.834300851439579</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>23.622945427121163</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="11">
         <v>7.2433796353250131</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="11">
         <v>26.646701718540228</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="12">
         <v>57.513026780986408</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>46.617003450958492</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="11">
         <v>5.536481690697646</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="11">
         <v>16.597626944677675</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>68.751112086333805</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="29.25" hidden="1" customHeight="1">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>14.838356875684312</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="11">
         <v>6.7663656177616955</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="11">
         <v>19.145194335480213</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="12">
         <v>40.749916828926217</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>33.407233424232167</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="11">
         <v>5.8918967336133283</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="11">
         <v>15.078106650211986</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="12">
         <v>54.377236808057482</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="11">
         <v>22.392744438222532</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="11">
         <v>18.495716476258757</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="11">
         <v>28.308581177615771</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="12">
         <v>69.197042092097064</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="11">
         <v>22.97952041022074</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="11">
         <v>4.4565407603216505</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="11">
         <v>19.523721436142562</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="12">
         <v>46.959782606684954</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="11">
         <v>2.1514153965203384</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="11">
         <v>3.3980299253452069</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="11">
         <v>30.883115616615601</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="12">
         <v>36.432560938481153</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="11">
         <v>6.0500515013197855</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="11">
         <v>1.9166108650378735</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="11">
         <v>16.097637492141697</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="12">
         <v>24.064299858499357</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="11">
         <v>4.8275810889834156</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="11">
         <v>2.0064057847976895</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="11">
         <v>20.739960164211311</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="12">
         <v>27.573947037992415</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="11">
         <v>8.6106035961317016</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="11">
         <v>2.0019748125840451</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="11">
         <v>10.582795175096022</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="12">
         <v>21.195373583811769</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="11">
         <v>13.348312147320595</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="11">
         <v>2.3016221243063897</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="11">
         <v>14.849727502408392</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="12">
         <v>30.499661774035374</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="11">
         <v>2.9031987081960482</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="11">
         <v>0.61887116495701755</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="11">
         <v>12.366670711332221</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="12">
         <v>15.888740584485287</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="11">
         <v>36.411215068972233</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="11">
         <v>1.2982751523517415</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="11">
         <v>7.2305625795030029</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="12">
         <v>44.940052800826976</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="11">
         <v>0.66066816156226049</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="11">
         <v>1.1274445800573356</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="11">
         <v>21.720662673970835</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="12">
         <v>23.508775415590431</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="11">
         <v>37.855178647500246</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="11">
         <v>26.207727555735183</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="11">
         <v>6.3383952855847694</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="12">
         <v>70.401301488820195</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="11">
         <v>18.293500714729166</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="11">
         <v>20.882132654616797</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="11">
         <v>26.237683349572162</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="12">
         <v>65.413316718918125</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="11">
         <v>3.8868121005410381</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="11">
         <v>3.6021218958218575</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="11">
         <v>16.601986070342505</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="12">
         <v>24.090920066705404</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="29.25" hidden="1" customHeight="1">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="11">
         <v>39.158899340934425</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="11">
         <v>0.14322127262889589</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="11">
         <v>1.3264493249630049</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="12">
         <v>40.628569938526326</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="11">
         <v>37.04572959457046</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="11">
         <v>7.1369887479907123E-3</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="11">
         <v>1.432155742096803</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="12">
         <v>38.485022325415258</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="11">
         <v>63.587604290822405</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="11">
         <v>1.7920143027413589</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="11">
         <v>0</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="12">
         <v>65.379618593563762</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="17">
         <v>38.692903704688305</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="17">
         <v>9.8033753174932272</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="17">
         <v>17.288591140082161</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="18">
         <v>65.784870162263701</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16" thickTop="1">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
-    </row>
-    <row r="30" spans="1:5" ht="15">
-      <c r="A30" s="25"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="24"/>
-    </row>
-    <row r="31" spans="1:5" ht="15">
-      <c r="A31" s="25"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="24"/>
-    </row>
-    <row r="32" spans="1:5" ht="15">
-      <c r="A32" s="25"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="24"/>
-    </row>
-    <row r="33" spans="1:5" ht="15">
-      <c r="A33" s="25"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="24"/>
-    </row>
-    <row r="34" spans="1:5" ht="15">
-      <c r="A34" s="25"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="24"/>
-    </row>
-    <row r="35" spans="1:5" ht="15">
-      <c r="A35" s="26"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="24"/>
+    <row r="29" spans="1:5" ht="17" thickTop="1">
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="21"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="21"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="21"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="21"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="20"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="21"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="20"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="22"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4568,9 +5499,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B2:G110"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.1640625" bestFit="1" customWidth="1"/>
@@ -4580,20 +5511,20 @@
       <c r="B2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="16">
+    <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -4610,7 +5541,7 @@
         <v>91.902786635166137</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="16">
+    <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
@@ -4627,7 +5558,7 @@
         <v>86.462423494897067</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="16">
+    <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
@@ -4644,7 +5575,7 @@
         <v>67.185936956006003</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="16">
+    <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
@@ -4661,7 +5592,7 @@
         <v>67.834300851439579</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="16">
+    <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -4678,7 +5609,7 @@
         <v>57.513026780986408</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="16">
+    <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
@@ -4695,7 +5626,7 @@
         <v>68.751112086333805</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="16">
+    <row r="9" spans="2:6">
       <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
@@ -4712,7 +5643,7 @@
         <v>40.749916828926217</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="16">
+    <row r="10" spans="2:6">
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
@@ -4729,7 +5660,7 @@
         <v>54.377236808057482</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="16">
+    <row r="11" spans="2:6">
       <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
@@ -4746,7 +5677,7 @@
         <v>69.197042092097064</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="16">
+    <row r="12" spans="2:6">
       <c r="B12" s="4" t="s">
         <v>17</v>
       </c>
@@ -4763,7 +5694,7 @@
         <v>46.959782606684954</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="16">
+    <row r="13" spans="2:6">
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
@@ -4780,7 +5711,7 @@
         <v>36.432560938481153</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="16">
+    <row r="14" spans="2:6">
       <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
@@ -4797,7 +5728,7 @@
         <v>24.064299858499357</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="16">
+    <row r="15" spans="2:6">
       <c r="B15" s="4" t="s">
         <v>20</v>
       </c>
@@ -4814,7 +5745,7 @@
         <v>27.573947037992415</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="16">
+    <row r="16" spans="2:6">
       <c r="B16" s="4" t="s">
         <v>21</v>
       </c>
@@ -4831,7 +5762,7 @@
         <v>21.195373583811769</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="16">
+    <row r="17" spans="2:7">
       <c r="B17" s="4" t="s">
         <v>22</v>
       </c>
@@ -4848,7 +5779,7 @@
         <v>30.499661774035374</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="16">
+    <row r="18" spans="2:7">
       <c r="B18" s="4" t="s">
         <v>23</v>
       </c>
@@ -4865,7 +5796,7 @@
         <v>15.888740584485287</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="16">
+    <row r="19" spans="2:7">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -4882,7 +5813,7 @@
         <v>44.940052800826976</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="16">
+    <row r="20" spans="2:7">
       <c r="B20" s="4" t="s">
         <v>25</v>
       </c>
@@ -4899,7 +5830,7 @@
         <v>23.508775415590431</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="16">
+    <row r="21" spans="2:7">
       <c r="B21" s="4" t="s">
         <v>26</v>
       </c>
@@ -4916,7 +5847,7 @@
         <v>70.401301488820195</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="16">
+    <row r="22" spans="2:7">
       <c r="B22" s="4" t="s">
         <v>27</v>
       </c>
@@ -4933,7 +5864,7 @@
         <v>65.413316718918125</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="16">
+    <row r="23" spans="2:7">
       <c r="B23" s="4" t="s">
         <v>28</v>
       </c>
@@ -4950,7 +5881,7 @@
         <v>24.090920066705404</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="16">
+    <row r="24" spans="2:7">
       <c r="B24" s="4" t="s">
         <v>29</v>
       </c>
@@ -4967,7 +5898,7 @@
         <v>40.628569938526326</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="16">
+    <row r="25" spans="2:7">
       <c r="B25" s="4" t="s">
         <v>30</v>
       </c>
@@ -4984,7 +5915,7 @@
         <v>38.485022325415258</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="16">
+    <row r="26" spans="2:7">
       <c r="B26" s="4" t="s">
         <v>31</v>
       </c>
@@ -5005,357 +5936,357 @@
       <c r="B32" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="34" t="s">
+      <c r="F32" s="26" t="s">
         <v>74</v>
       </c>
       <c r="G32" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="16">
+    <row r="33" spans="2:7">
       <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="5">
         <v>91.902786635166137</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="28">
         <v>91.902786635166137</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="16">
+    <row r="34" spans="2:7">
       <c r="B34" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="5">
         <v>86.462423494897067</v>
       </c>
-      <c r="F34" s="35" t="s">
+      <c r="F34" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="28">
         <v>86.462423494897067</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="16">
+    <row r="35" spans="2:7">
       <c r="B35" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="5">
         <v>67.185936956006003</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="28">
         <v>70.401301488820195</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="16">
+    <row r="36" spans="2:7">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="5">
         <v>67.834300851439579</v>
       </c>
-      <c r="F36" s="35" t="s">
+      <c r="F36" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="28">
         <v>69.197042092097064</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="16">
+    <row r="37" spans="2:7">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5">
         <v>57.513026780986408</v>
       </c>
-      <c r="F37" s="35" t="s">
+      <c r="F37" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="28">
         <v>68.751112086333805</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16">
+    <row r="38" spans="2:7">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="5">
         <v>68.751112086333805</v>
       </c>
-      <c r="F38" s="35" t="s">
+      <c r="F38" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="G38" s="36">
+      <c r="G38" s="28">
         <v>67.834300851439579</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="16">
+    <row r="39" spans="2:7">
       <c r="B39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="5">
         <v>40.749916828926217</v>
       </c>
-      <c r="F39" s="35" t="s">
+      <c r="F39" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="36">
+      <c r="G39" s="28">
         <v>67.185936956006003</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="16">
+    <row r="40" spans="2:7">
       <c r="B40" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="5">
         <v>54.377236808057482</v>
       </c>
-      <c r="F40" s="35" t="s">
+      <c r="F40" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="G40" s="36">
+      <c r="G40" s="28">
         <v>65.413316718918125</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="16">
+    <row r="41" spans="2:7">
       <c r="B41" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="5">
         <v>69.197042092097064</v>
       </c>
-      <c r="F41" s="35" t="s">
+      <c r="F41" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G41" s="36">
+      <c r="G41" s="28">
         <v>65.379618593563762</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="16">
+    <row r="42" spans="2:7">
       <c r="B42" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C42" s="5">
         <v>46.959782606684954</v>
       </c>
-      <c r="F42" s="35" t="s">
+      <c r="F42" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="36">
+      <c r="G42" s="28">
         <v>57.513026780986408</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="16">
+    <row r="43" spans="2:7">
       <c r="B43" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="5">
         <v>36.432560938481153</v>
       </c>
-      <c r="F43" s="35" t="s">
+      <c r="F43" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G43" s="36">
+      <c r="G43" s="28">
         <v>54.377236808057482</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="16">
+    <row r="44" spans="2:7">
       <c r="B44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="5">
         <v>24.064299858499357</v>
       </c>
-      <c r="F44" s="35" t="s">
+      <c r="F44" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="36">
+      <c r="G44" s="28">
         <v>46.959782606684954</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="16">
+    <row r="45" spans="2:7">
       <c r="B45" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C45" s="5">
         <v>27.573947037992415</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F45" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="G45" s="36">
+      <c r="G45" s="28">
         <v>44.940052800826976</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="16">
+    <row r="46" spans="2:7">
       <c r="B46" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="5">
         <v>21.195373583811769</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G46" s="36">
+      <c r="G46" s="28">
         <v>40.749916828926217</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="16">
+    <row r="47" spans="2:7">
       <c r="B47" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C47" s="5">
         <v>30.499661774035374</v>
       </c>
-      <c r="F47" s="35" t="s">
+      <c r="F47" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G47" s="36">
+      <c r="G47" s="28">
         <v>40.628569938526326</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="16">
+    <row r="48" spans="2:7">
       <c r="B48" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="5">
         <v>15.888740584485287</v>
       </c>
-      <c r="F48" s="35" t="s">
+      <c r="F48" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G48" s="36">
+      <c r="G48" s="28">
         <v>38.485022325415258</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="16">
+    <row r="49" spans="2:7">
       <c r="B49" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="5">
         <v>44.940052800826976</v>
       </c>
-      <c r="F49" s="35" t="s">
+      <c r="F49" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G49" s="36">
+      <c r="G49" s="28">
         <v>36.432560938481153</v>
       </c>
     </row>
-    <row r="50" spans="2:7" ht="16">
+    <row r="50" spans="2:7">
       <c r="B50" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C50" s="5">
         <v>23.508775415590431</v>
       </c>
-      <c r="F50" s="35" t="s">
+      <c r="F50" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G50" s="36">
+      <c r="G50" s="28">
         <v>30.499661774035374</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="16">
+    <row r="51" spans="2:7">
       <c r="B51" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C51" s="5">
         <v>70.401301488820195</v>
       </c>
-      <c r="F51" s="35" t="s">
+      <c r="F51" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="36">
+      <c r="G51" s="28">
         <v>27.573947037992415</v>
       </c>
     </row>
-    <row r="52" spans="2:7" ht="16">
+    <row r="52" spans="2:7">
       <c r="B52" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="5">
         <v>65.413316718918125</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G52" s="36">
+      <c r="G52" s="28">
         <v>24.090920066705404</v>
       </c>
     </row>
-    <row r="53" spans="2:7" ht="16">
+    <row r="53" spans="2:7">
       <c r="B53" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C53" s="5">
         <v>24.090920066705404</v>
       </c>
-      <c r="F53" s="35" t="s">
+      <c r="F53" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G53" s="36">
+      <c r="G53" s="28">
         <v>24.064299858499357</v>
       </c>
     </row>
-    <row r="54" spans="2:7" ht="16">
+    <row r="54" spans="2:7">
       <c r="B54" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C54" s="5">
         <v>40.628569938526326</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="F54" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G54" s="36">
+      <c r="G54" s="28">
         <v>23.508775415590431</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="16">
+    <row r="55" spans="2:7">
       <c r="B55" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C55" s="5">
         <v>38.485022325415258</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F55" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="36">
+      <c r="G55" s="28">
         <v>21.195373583811769</v>
       </c>
     </row>
-    <row r="56" spans="2:7" ht="16">
+    <row r="56" spans="2:7">
       <c r="B56" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C56" s="5">
         <v>65.379618593563762</v>
       </c>
-      <c r="F56" s="35" t="s">
+      <c r="F56" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="G56" s="36">
+      <c r="G56" s="28">
         <v>15.888740584485287</v>
       </c>
     </row>
     <row r="57" spans="2:7">
-      <c r="F57" s="35" t="s">
+      <c r="F57" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="G57" s="36">
+      <c r="G57" s="28">
         <v>1179.4357262662666</v>
       </c>
     </row>
@@ -5363,17 +6294,17 @@
       <c r="B64" t="s">
         <v>73</v>
       </c>
-      <c r="C64" s="33" t="s">
+      <c r="C64" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D64" s="33" t="s">
+      <c r="D64" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E64" s="33" t="s">
+      <c r="E64" s="25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="65" spans="2:5" ht="16">
+    <row r="65" spans="2:5">
       <c r="B65" s="4" t="s">
         <v>8</v>
       </c>
@@ -5387,7 +6318,7 @@
         <v>7.5239000366335507</v>
       </c>
     </row>
-    <row r="66" spans="2:5" ht="16">
+    <row r="66" spans="2:5">
       <c r="B66" s="4" t="s">
         <v>9</v>
       </c>
@@ -5401,7 +6332,7 @@
         <v>0.89632658778486352</v>
       </c>
     </row>
-    <row r="67" spans="2:5" ht="16">
+    <row r="67" spans="2:5">
       <c r="B67" s="4" t="s">
         <v>10</v>
       </c>
@@ -5415,7 +6346,7 @@
         <v>25.351012271734341</v>
       </c>
     </row>
-    <row r="68" spans="2:5" ht="16">
+    <row r="68" spans="2:5">
       <c r="B68" s="4" t="s">
         <v>11</v>
       </c>
@@ -5429,7 +6360,7 @@
         <v>33.446598319816452</v>
       </c>
     </row>
-    <row r="69" spans="2:5" ht="16">
+    <row r="69" spans="2:5">
       <c r="B69" s="4" t="s">
         <v>12</v>
       </c>
@@ -5443,7 +6374,7 @@
         <v>26.646701718540228</v>
       </c>
     </row>
-    <row r="70" spans="2:5" ht="16">
+    <row r="70" spans="2:5">
       <c r="B70" s="4" t="s">
         <v>13</v>
       </c>
@@ -5457,7 +6388,7 @@
         <v>16.597626944677675</v>
       </c>
     </row>
-    <row r="71" spans="2:5" ht="16">
+    <row r="71" spans="2:5">
       <c r="B71" s="4" t="s">
         <v>14</v>
       </c>
@@ -5471,7 +6402,7 @@
         <v>19.145194335480213</v>
       </c>
     </row>
-    <row r="72" spans="2:5" ht="16">
+    <row r="72" spans="2:5">
       <c r="B72" s="4" t="s">
         <v>15</v>
       </c>
@@ -5485,7 +6416,7 @@
         <v>15.078106650211986</v>
       </c>
     </row>
-    <row r="73" spans="2:5" ht="16">
+    <row r="73" spans="2:5">
       <c r="B73" s="4" t="s">
         <v>16</v>
       </c>
@@ -5499,7 +6430,7 @@
         <v>28.308581177615771</v>
       </c>
     </row>
-    <row r="74" spans="2:5" ht="16">
+    <row r="74" spans="2:5">
       <c r="B74" s="4" t="s">
         <v>17</v>
       </c>
@@ -5513,7 +6444,7 @@
         <v>19.523721436142562</v>
       </c>
     </row>
-    <row r="75" spans="2:5" ht="16">
+    <row r="75" spans="2:5">
       <c r="B75" s="4" t="s">
         <v>18</v>
       </c>
@@ -5527,7 +6458,7 @@
         <v>30.883115616615601</v>
       </c>
     </row>
-    <row r="76" spans="2:5" ht="16">
+    <row r="76" spans="2:5">
       <c r="B76" s="4" t="s">
         <v>19</v>
       </c>
@@ -5541,7 +6472,7 @@
         <v>16.097637492141697</v>
       </c>
     </row>
-    <row r="77" spans="2:5" ht="16">
+    <row r="77" spans="2:5">
       <c r="B77" s="4" t="s">
         <v>20</v>
       </c>
@@ -5555,7 +6486,7 @@
         <v>20.739960164211311</v>
       </c>
     </row>
-    <row r="78" spans="2:5" ht="16">
+    <row r="78" spans="2:5">
       <c r="B78" s="4" t="s">
         <v>21</v>
       </c>
@@ -5569,7 +6500,7 @@
         <v>10.582795175096022</v>
       </c>
     </row>
-    <row r="79" spans="2:5" ht="16">
+    <row r="79" spans="2:5">
       <c r="B79" s="4" t="s">
         <v>22</v>
       </c>
@@ -5583,7 +6514,7 @@
         <v>14.849727502408392</v>
       </c>
     </row>
-    <row r="80" spans="2:5" ht="16">
+    <row r="80" spans="2:5">
       <c r="B80" s="4" t="s">
         <v>23</v>
       </c>
@@ -5597,7 +6528,7 @@
         <v>12.366670711332221</v>
       </c>
     </row>
-    <row r="81" spans="2:5" ht="16">
+    <row r="81" spans="2:5">
       <c r="B81" s="4" t="s">
         <v>24</v>
       </c>
@@ -5611,7 +6542,7 @@
         <v>7.2305625795030029</v>
       </c>
     </row>
-    <row r="82" spans="2:5" ht="16">
+    <row r="82" spans="2:5">
       <c r="B82" s="4" t="s">
         <v>25</v>
       </c>
@@ -5625,7 +6556,7 @@
         <v>21.720662673970835</v>
       </c>
     </row>
-    <row r="83" spans="2:5" ht="16">
+    <row r="83" spans="2:5">
       <c r="B83" s="4" t="s">
         <v>26</v>
       </c>
@@ -5639,7 +6570,7 @@
         <v>6.3383952855847694</v>
       </c>
     </row>
-    <row r="84" spans="2:5" ht="16">
+    <row r="84" spans="2:5">
       <c r="B84" s="4" t="s">
         <v>27</v>
       </c>
@@ -5653,7 +6584,7 @@
         <v>26.237683349572162</v>
       </c>
     </row>
-    <row r="85" spans="2:5" ht="16">
+    <row r="85" spans="2:5">
       <c r="B85" s="4" t="s">
         <v>28</v>
       </c>
@@ -5667,7 +6598,7 @@
         <v>16.601986070342505</v>
       </c>
     </row>
-    <row r="86" spans="2:5" ht="16">
+    <row r="86" spans="2:5">
       <c r="B86" s="4" t="s">
         <v>29</v>
       </c>
@@ -5681,7 +6612,7 @@
         <v>1.3264493249630049</v>
       </c>
     </row>
-    <row r="87" spans="2:5" ht="16">
+    <row r="87" spans="2:5">
       <c r="B87" s="4" t="s">
         <v>30</v>
       </c>
@@ -5695,7 +6626,7 @@
         <v>1.432155742096803</v>
       </c>
     </row>
-    <row r="88" spans="2:5" ht="16">
+    <row r="88" spans="2:5">
       <c r="B88" s="4" t="s">
         <v>31</v>
       </c>
@@ -5709,7 +6640,74 @@
         <v>0</v>
       </c>
     </row>
+    <row r="103" spans="2:3" ht="28">
+      <c r="B103" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3">
+      <c r="B104" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="5">
+        <v>91.902786635166137</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3">
+      <c r="B105" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="5">
+        <v>86.462423494897067</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3">
+      <c r="B106" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="5">
+        <v>68.751112086333805</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3">
+      <c r="B107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="5">
+        <v>67.834300851439579</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="B108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="5">
+        <v>67.185936956006003</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3">
+      <c r="B109" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" s="5">
+        <v>57.513026780986408</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3">
+      <c r="B110" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="5">
+        <v>40.749916828926217</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B104:C110">
+    <sortCondition descending="1" ref="C104:C110"/>
+  </sortState>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
